--- a/artfynd/A 26186-2026 artfynd.xlsx
+++ b/artfynd/A 26186-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125056371</v>
+        <v>125056377</v>
       </c>
       <c r="B2" t="n">
-        <v>95535</v>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464952</v>
+        <v>465002</v>
       </c>
       <c r="R2" t="n">
-        <v>6640859</v>
+        <v>6640965</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,6 +748,11 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Endast protonema</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -756,6 +761,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -772,32 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125056377</v>
+        <v>125056373</v>
       </c>
       <c r="B3" t="n">
-        <v>95751</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465002</v>
+        <v>464963</v>
       </c>
       <c r="R3" t="n">
-        <v>6640965</v>
+        <v>6640868</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Endast protonema</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +904,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125056373</v>
+        <v>125056371</v>
       </c>
       <c r="B4" t="n">
-        <v>91198</v>
+        <v>96338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464963</v>
+        <v>464952</v>
       </c>
       <c r="R4" t="n">
-        <v>6640868</v>
+        <v>6640859</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,21 +985,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125056378</v>
+        <v>125056384</v>
       </c>
       <c r="B5" t="n">
-        <v>80008</v>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465039</v>
+        <v>465199</v>
       </c>
       <c r="R5" t="n">
-        <v>6640973</v>
+        <v>6640872</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,21 +1083,6 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1110,6 +1095,230 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125056376</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vintersjöhöjden, Gåsborn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>464972</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6641006</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gåsborn</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125056378</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vintersjöhöjden, Gåsborn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>465039</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6640973</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gåsborn</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26186-2026 artfynd.xlsx
+++ b/artfynd/A 26186-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125056377</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125056373</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125056371</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125056384</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125056376</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,8 +1349,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125056378</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>